--- a/artfynd/A 38930-2025 artfynd.xlsx
+++ b/artfynd/A 38930-2025 artfynd.xlsx
@@ -3800,10 +3800,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>133851104</v>
+        <v>133850774</v>
       </c>
       <c r="B32" t="n">
-        <v>83336</v>
+        <v>91960</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3811,21 +3811,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>308</v>
+        <v>1202</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3835,10 +3835,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>611745</v>
+        <v>611669</v>
       </c>
       <c r="R32" t="n">
-        <v>7158685</v>
+        <v>7158675</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3875,7 +3875,7 @@
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>Datum osäkert, men mellan 2024-05-05 och 2025-10-46</t>
+          <t>Datum osäkert, men mellan 2024-05-05 och 2025-10-54</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3902,10 +3902,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>133850774</v>
+        <v>133851104</v>
       </c>
       <c r="B33" t="n">
-        <v>91960</v>
+        <v>83336</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3913,21 +3913,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1202</v>
+        <v>308</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3937,10 +3937,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>611669</v>
+        <v>611745</v>
       </c>
       <c r="R33" t="n">
-        <v>7158675</v>
+        <v>7158685</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3977,7 +3977,7 @@
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>Datum osäkert, men mellan 2024-05-05 och 2025-10-54</t>
+          <t>Datum osäkert, men mellan 2024-05-05 och 2025-10-46</t>
         </is>
       </c>
       <c r="AD33" t="b">

--- a/artfynd/A 38930-2025 artfynd.xlsx
+++ b/artfynd/A 38930-2025 artfynd.xlsx
@@ -2893,7 +2893,7 @@
         <v>133850916</v>
       </c>
       <c r="B23" t="n">
-        <v>92231</v>
+        <v>92238</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2995,7 +2995,7 @@
         <v>133851027</v>
       </c>
       <c r="B24" t="n">
-        <v>91980</v>
+        <v>91987</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3090,10 +3090,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>133850775</v>
+        <v>133850797</v>
       </c>
       <c r="B25" t="n">
-        <v>91960</v>
+        <v>91967</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3125,10 +3125,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>611818</v>
+        <v>611695</v>
       </c>
       <c r="R25" t="n">
-        <v>7158675</v>
+        <v>7158387</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3165,7 +3165,7 @@
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>Datum osäkert, men mellan 2024-05-05 och 2025-10-53</t>
+          <t>Datum osäkert, men mellan 2024-05-05 och 2025-10-33</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3192,10 +3192,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>133850797</v>
+        <v>133850775</v>
       </c>
       <c r="B26" t="n">
-        <v>91960</v>
+        <v>91967</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3227,10 +3227,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>611695</v>
+        <v>611818</v>
       </c>
       <c r="R26" t="n">
-        <v>7158387</v>
+        <v>7158675</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3267,7 +3267,7 @@
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>Datum osäkert, men mellan 2024-05-05 och 2025-10-33</t>
+          <t>Datum osäkert, men mellan 2024-05-05 och 2025-10-53</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3297,7 +3297,7 @@
         <v>133850778</v>
       </c>
       <c r="B27" t="n">
-        <v>91960</v>
+        <v>91967</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3399,7 +3399,7 @@
         <v>133851001</v>
       </c>
       <c r="B28" t="n">
-        <v>91956</v>
+        <v>91963</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3501,7 +3501,7 @@
         <v>133850741</v>
       </c>
       <c r="B29" t="n">
-        <v>83344</v>
+        <v>83351</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3603,7 +3603,7 @@
         <v>133851042</v>
       </c>
       <c r="B30" t="n">
-        <v>91980</v>
+        <v>91987</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3701,7 +3701,7 @@
         <v>133850794</v>
       </c>
       <c r="B31" t="n">
-        <v>91960</v>
+        <v>91967</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3800,10 +3800,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>133850774</v>
+        <v>133851104</v>
       </c>
       <c r="B32" t="n">
-        <v>91960</v>
+        <v>83343</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3811,21 +3811,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1202</v>
+        <v>308</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3835,10 +3835,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>611669</v>
+        <v>611745</v>
       </c>
       <c r="R32" t="n">
-        <v>7158675</v>
+        <v>7158685</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3875,7 +3875,7 @@
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>Datum osäkert, men mellan 2024-05-05 och 2025-10-54</t>
+          <t>Datum osäkert, men mellan 2024-05-05 och 2025-10-46</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3902,10 +3902,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>133851104</v>
+        <v>133850774</v>
       </c>
       <c r="B33" t="n">
-        <v>83336</v>
+        <v>91967</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3913,21 +3913,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>308</v>
+        <v>1202</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3937,10 +3937,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>611745</v>
+        <v>611669</v>
       </c>
       <c r="R33" t="n">
-        <v>7158685</v>
+        <v>7158675</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3977,7 +3977,7 @@
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>Datum osäkert, men mellan 2024-05-05 och 2025-10-46</t>
+          <t>Datum osäkert, men mellan 2024-05-05 och 2025-10-54</t>
         </is>
       </c>
       <c r="AD33" t="b">

--- a/artfynd/A 38930-2025 artfynd.xlsx
+++ b/artfynd/A 38930-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY33"/>
+  <dimension ref="A1:AY32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>346338</v>
+        <v>126390906</v>
       </c>
       <c r="B2" t="n">
-        <v>89388</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83299</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,34 +686,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1108</v>
+        <v>308</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Riprismyran, Ås lm</t>
+          <t>Riprismyrtjärnen, Ås lm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>611785.6171783018</v>
+        <v>611966</v>
       </c>
       <c r="R2" t="n">
-        <v>7158265.438456634</v>
+        <v>7158606</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -745,22 +740,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2012-09-30</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-07-03</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2012-09-30</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-07-03</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -771,36 +756,26 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
-      </c>
-      <c r="AH2" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>SCA Naturvärdesinventeringar</t>
+          <t>Manne Frih</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Via SCA Naturvärdesinventeringar</t>
+          <t>Manne Frih</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>92843</v>
+        <v>133851104</v>
       </c>
       <c r="B3" t="n">
-        <v>76504</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83350</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -808,34 +783,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>314</v>
+        <v>308</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vitskaftad svartspik</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Chaenothecopsis viridialba</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Kremp.) A.F.W.Schmidt</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Riprismyran, Ås lm</t>
+          <t>Skogen, Ås lm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>611649.3780212309</v>
+        <v>611745</v>
       </c>
       <c r="R3" t="n">
-        <v>7158686.511087483</v>
+        <v>7158685</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -862,22 +837,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2012-09-30</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-05-01</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2012-09-30</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-05-01</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Datum osäkert, men mellan 2024-05-05 och 2025-10-46</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -888,58 +858,48 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
-      </c>
-      <c r="AH3" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>SCA Naturvärdesinventeringar</t>
+          <t>Lukas Holmström</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Via SCA Naturvärdesinventeringar</t>
+          <t>Lukas Holmström</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>363943</v>
+        <v>92843</v>
       </c>
       <c r="B4" t="n">
-        <v>81236</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78350</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1312</v>
+        <v>314</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Vitskaftad svartspik</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Chaenothecopsis viridialba</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Kremp.) A.F.W.Schmidt</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -949,10 +909,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>611675.120617875</v>
+        <v>611649</v>
       </c>
       <c r="R4" t="n">
-        <v>7158713.733611524</v>
+        <v>7158687</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -982,19 +942,9 @@
           <t>2012-09-30</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2012-09-30</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1026,10 +976,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>126382905</v>
+        <v>209906</v>
       </c>
       <c r="B5" t="n">
-        <v>91263</v>
+        <v>92208</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1037,37 +987,37 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5432</v>
+        <v>658</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Bredmyran, Bredmyran, Ås lm</t>
+          <t>Riprismyran, Ås lm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>611758</v>
+        <v>611598</v>
       </c>
       <c r="R5" t="n">
-        <v>7158361</v>
+        <v>7158658</v>
       </c>
       <c r="S5" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1091,22 +1041,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-07-03</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>10:18</t>
+          <t>2012-09-30</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-07-03</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>10:18</t>
+          <t>2012-09-30</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1117,61 +1057,66 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Tove Lundmark</t>
+          <t>SCA Naturvärdesinventeringar</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Tove Lundmark</t>
+          <t>Via SCA Naturvärdesinventeringar</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>126390902</v>
+        <v>133850916</v>
       </c>
       <c r="B6" t="n">
-        <v>5196</v>
+        <v>92245</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>105930</v>
+        <v>658</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Riprismyrtjärnen, Ås lm</t>
+          <t>Skogen, Ås lm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>611913</v>
+        <v>611665</v>
       </c>
       <c r="R6" t="n">
-        <v>7158583</v>
+        <v>7158679</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1198,12 +1143,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-07-03</t>
+          <t>2024-05-01</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2025-07-03</t>
+          <t>2024-05-01</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Datum osäkert, men mellan 2024-05-05 och 2025-10-47</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1218,22 +1168,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Manne Frih</t>
+          <t>Lukas Holmström</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Manne Frih</t>
+          <t>Lukas Holmström</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>126382400</v>
+        <v>346338</v>
       </c>
       <c r="B7" t="n">
-        <v>57657</v>
+        <v>91905</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1241,37 +1191,37 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Bredmyran, Bredmyran, Ås lm</t>
+          <t>Riprismyran, Ås lm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>611773</v>
+        <v>611786</v>
       </c>
       <c r="R7" t="n">
-        <v>7158412</v>
+        <v>7158265</v>
       </c>
       <c r="S7" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1295,27 +1245,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-07-03</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>10:55</t>
+          <t>2012-09-30</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2025-07-03</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>10:55</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Färsk ringhack yngre än 5 år</t>
+          <t>2012-09-30</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1326,61 +1261,66 @@
       </c>
       <c r="AG7" t="b">
         <v>0</v>
+      </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Carl Wiking</t>
+          <t>SCA Naturvärdesinventeringar</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Carl Wiking</t>
+          <t>Via SCA Naturvärdesinventeringar</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>126390896</v>
+        <v>133851001</v>
       </c>
       <c r="B8" t="n">
-        <v>91603</v>
+        <v>91970</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>2062</v>
+        <v>1108</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Riprismyrtjärnen, Ås lm</t>
+          <t>Skogen, Ås lm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>611664</v>
+        <v>611791</v>
       </c>
       <c r="R8" t="n">
-        <v>7158677</v>
+        <v>7158655</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1407,12 +1347,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-07-03</t>
+          <t>2024-05-01</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2025-07-03</t>
+          <t>2024-05-01</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Datum osäkert, men mellan 2024-05-05 och 2025-10-70</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1427,22 +1372,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Manne Frih</t>
+          <t>Lukas Holmström</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Manne Frih</t>
+          <t>Lukas Holmström</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>126390906</v>
+        <v>424379</v>
       </c>
       <c r="B9" t="n">
-        <v>75067</v>
+        <v>91909</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1450,34 +1395,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>308</v>
+        <v>1202</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Riprismyrtjärnen, Ås lm</t>
+          <t>Riprismyran, Ås lm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>611966</v>
+        <v>611598</v>
       </c>
       <c r="R9" t="n">
-        <v>7158606</v>
+        <v>7158658</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1504,12 +1449,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-07-03</t>
+          <t>2012-09-30</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2025-07-03</t>
+          <t>2012-09-30</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1520,26 +1465,31 @@
       </c>
       <c r="AG9" t="b">
         <v>0</v>
+      </c>
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Manne Frih</t>
+          <t>SCA Naturvärdesinventeringar</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Manne Frih</t>
+          <t>Via SCA Naturvärdesinventeringar</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>126390901</v>
+        <v>126384810</v>
       </c>
       <c r="B10" t="n">
-        <v>57657</v>
+        <v>91909</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1547,45 +1497,37 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Riprismyrtjärnen, Ås lm</t>
+          <t>Riprismyrtjärnen, Riprismyrtjärnen, Ås lm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>611763</v>
+        <v>611646</v>
       </c>
       <c r="R10" t="n">
-        <v>7158409</v>
+        <v>7158656</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1612,9 +1554,19 @@
           <t>2025-07-03</t>
         </is>
       </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>11:30</t>
+        </is>
+      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-07-03</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1629,22 +1581,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Manne Frih</t>
+          <t>Tove Lundmark</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Manne Frih</t>
+          <t>Tove Lundmark</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>126385273</v>
+        <v>126390903</v>
       </c>
       <c r="B11" t="n">
-        <v>82792</v>
+        <v>91909</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1652,37 +1604,37 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1312</v>
+        <v>1202</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Riprismyrtjärnen, Riprismyrtjärnen, Ås lm</t>
+          <t>Riprismyrtjärnen, Ås lm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>611695</v>
+        <v>611899</v>
       </c>
       <c r="R11" t="n">
-        <v>7158675</v>
+        <v>7158587</v>
       </c>
       <c r="S11" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1709,19 +1661,9 @@
           <t>2025-07-03</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>13:31</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-07-03</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>13:31</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1736,57 +1678,57 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Carl Wiking</t>
+          <t>Manne Frih</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Carl Wiking</t>
+          <t>Manne Frih</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>126390905</v>
+        <v>133850774</v>
       </c>
       <c r="B12" t="n">
-        <v>75059</v>
+        <v>91974</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6439</v>
+        <v>1202</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Riprismyrtjärnen, Ås lm</t>
+          <t>Skogen, Ås lm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>611966</v>
+        <v>611669</v>
       </c>
       <c r="R12" t="n">
-        <v>7158606</v>
+        <v>7158675</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1813,12 +1755,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-07-03</t>
+          <t>2024-05-01</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2025-07-03</t>
+          <t>2024-05-01</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Datum osäkert, men mellan 2024-05-05 och 2025-10-54</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1833,22 +1780,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Manne Frih</t>
+          <t>Lukas Holmström</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Manne Frih</t>
+          <t>Lukas Holmström</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>126384755</v>
+        <v>133850775</v>
       </c>
       <c r="B13" t="n">
-        <v>57657</v>
+        <v>91974</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1856,37 +1803,37 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Riprismyrtjärnen, Riprismyrtjärnen, Ås lm</t>
+          <t>Skogen, Ås lm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>611634</v>
+        <v>611818</v>
       </c>
       <c r="R13" t="n">
-        <v>7158666</v>
+        <v>7158675</v>
       </c>
       <c r="S13" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1910,22 +1857,17 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-07-03</t>
-        </is>
-      </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>11:30</t>
+          <t>2024-05-01</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2025-07-03</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>11:30</t>
+          <t>2024-05-01</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Datum osäkert, men mellan 2024-05-05 och 2025-10-53</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1940,22 +1882,22 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Tove Lundmark</t>
+          <t>Lukas Holmström</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Tove Lundmark</t>
+          <t>Lukas Holmström</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>126390904</v>
+        <v>133850778</v>
       </c>
       <c r="B14" t="n">
-        <v>91263</v>
+        <v>91974</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1963,34 +1905,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Riprismyrtjärnen, Ås lm</t>
+          <t>Skogen, Ås lm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>611899</v>
+        <v>611840</v>
       </c>
       <c r="R14" t="n">
-        <v>7158587</v>
+        <v>7158308</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2017,12 +1959,17 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-07-03</t>
+          <t>2024-05-01</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2025-07-03</t>
+          <t>2024-05-01</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Datum osäkert, men mellan 2024-05-05 och 2025-10-51</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2037,60 +1984,60 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Manne Frih</t>
+          <t>Lukas Holmström</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Manne Frih</t>
+          <t>Lukas Holmström</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>126380896</v>
+        <v>133850794</v>
       </c>
       <c r="B15" t="n">
-        <v>75059</v>
+        <v>91974</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6439</v>
+        <v>1202</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Riprismyrtjärnen, Riprismyrtjärnen, Ås lm</t>
+          <t>Skogen, Ås lm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>611946</v>
+        <v>611791</v>
       </c>
       <c r="R15" t="n">
-        <v>7158610</v>
+        <v>7158655</v>
       </c>
       <c r="S15" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2114,22 +2061,17 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-07-03</t>
-        </is>
-      </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>10:09</t>
+          <t>2024-05-01</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2025-07-03</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>10:09</t>
+          <t>2024-05-01</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Datum osäkert, men mellan 2024-05-05 och 2025-10-36</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2144,22 +2086,22 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Carl Wiking</t>
+          <t>Lukas Holmström</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Carl Wiking</t>
+          <t>Lukas Holmström</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>126390897</v>
+        <v>133850797</v>
       </c>
       <c r="B16" t="n">
-        <v>75075</v>
+        <v>91974</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2167,34 +2109,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6440</v>
+        <v>1202</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Riprismyrtjärnen, Ås lm</t>
+          <t>Skogen, Ås lm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>611656</v>
+        <v>611695</v>
       </c>
       <c r="R16" t="n">
-        <v>7158656</v>
+        <v>7158387</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2221,12 +2163,17 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-07-03</t>
+          <t>2024-05-01</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2025-07-03</t>
+          <t>2024-05-01</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Datum osäkert, men mellan 2024-05-05 och 2025-10-33</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2241,57 +2188,57 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Manne Frih</t>
+          <t>Lukas Holmström</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Manne Frih</t>
+          <t>Lukas Holmström</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>126390900</v>
+        <v>363943</v>
       </c>
       <c r="B17" t="n">
-        <v>5176</v>
+        <v>83173</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100526</v>
+        <v>1312</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Riprismyrtjärnen, Ås lm</t>
+          <t>Riprismyran, Ås lm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>611671</v>
+        <v>611675</v>
       </c>
       <c r="R17" t="n">
-        <v>7158434</v>
+        <v>7158714</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2318,12 +2265,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-07-03</t>
+          <t>2012-09-30</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2025-07-03</t>
+          <t>2012-09-30</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2334,26 +2281,31 @@
       </c>
       <c r="AG17" t="b">
         <v>0</v>
+      </c>
+      <c r="AH17" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Manne Frih</t>
+          <t>SCA Naturvärdesinventeringar</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Manne Frih</t>
+          <t>Via SCA Naturvärdesinventeringar</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>126390903</v>
+        <v>126385273</v>
       </c>
       <c r="B18" t="n">
-        <v>91245</v>
+        <v>83173</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2361,37 +2313,37 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1202</v>
+        <v>1312</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Riprismyrtjärnen, Ås lm</t>
+          <t>Riprismyrtjärnen, Riprismyrtjärnen, Ås lm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>611899</v>
+        <v>611695</v>
       </c>
       <c r="R18" t="n">
-        <v>7158587</v>
+        <v>7158675</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2418,9 +2370,19 @@
           <t>2025-07-03</t>
         </is>
       </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>13:31</t>
+        </is>
+      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-07-03</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2435,60 +2397,60 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Manne Frih</t>
+          <t>Carl Wiking</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Manne Frih</t>
+          <t>Carl Wiking</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>126382580</v>
+        <v>126390896</v>
       </c>
       <c r="B19" t="n">
-        <v>57657</v>
+        <v>92281</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>2062</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Riprismyrtjärnen, Riprismyrtjärnen, Ås lm</t>
+          <t>Riprismyrtjärnen, Ås lm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>611675</v>
+        <v>611664</v>
       </c>
       <c r="R19" t="n">
-        <v>7158457</v>
+        <v>7158677</v>
       </c>
       <c r="S19" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2515,24 +2477,9 @@
           <t>2025-07-03</t>
         </is>
       </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>11:05</t>
-        </is>
-      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-07-03</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>11:05</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett yngre än 5 år</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2547,22 +2494,22 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Carl Wiking</t>
+          <t>Manne Frih</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Carl Wiking</t>
+          <t>Manne Frih</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>126384810</v>
+        <v>126381047</v>
       </c>
       <c r="B20" t="n">
-        <v>91245</v>
+        <v>78730</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2570,21 +2517,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1202</v>
+        <v>6437</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2594,13 +2541,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>611646</v>
+        <v>611933</v>
       </c>
       <c r="R20" t="n">
-        <v>7158656</v>
+        <v>7158544</v>
       </c>
       <c r="S20" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2629,7 +2576,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>10:18</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2639,7 +2586,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>10:18</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2666,53 +2613,48 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>126383125</v>
+        <v>126380896</v>
       </c>
       <c r="B21" t="n">
-        <v>57657</v>
+        <v>83290</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>6439</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Bredmyran, Bredmyran, Ås lm</t>
+          <t>Riprismyrtjärnen, Riprismyrtjärnen, Ås lm</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>611839</v>
+        <v>611946</v>
       </c>
       <c r="R21" t="n">
-        <v>7158341</v>
+        <v>7158610</v>
       </c>
       <c r="S21" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2741,7 +2683,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>10:09</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2751,7 +2693,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>10:09</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2766,65 +2708,60 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Tove Lundmark</t>
+          <t>Carl Wiking</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Tove Lundmark</t>
+          <t>Carl Wiking</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>126383064</v>
+        <v>126390905</v>
       </c>
       <c r="B22" t="n">
-        <v>57657</v>
+        <v>83290</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>6439</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Bredmyran, Bredmyran, Ås lm</t>
+          <t>Riprismyrtjärnen, Ås lm</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>611800</v>
+        <v>611966</v>
       </c>
       <c r="R22" t="n">
-        <v>7158320</v>
+        <v>7158606</v>
       </c>
       <c r="S22" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2851,19 +2788,9 @@
           <t>2025-07-03</t>
         </is>
       </c>
-      <c r="Z22" t="inlineStr">
-        <is>
-          <t>10:18</t>
-        </is>
-      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-07-03</t>
-        </is>
-      </c>
-      <c r="AB22" t="inlineStr">
-        <is>
-          <t>10:18</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2878,22 +2805,22 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Tove Lundmark</t>
+          <t>Manne Frih</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Tove Lundmark</t>
+          <t>Manne Frih</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>133850916</v>
+        <v>126390897</v>
       </c>
       <c r="B23" t="n">
-        <v>92238</v>
+        <v>83307</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2901,34 +2828,34 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>658</v>
+        <v>6440</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Skogen, Ås lm</t>
+          <t>Riprismyrtjärnen, Ås lm</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>611665</v>
+        <v>611656</v>
       </c>
       <c r="R23" t="n">
-        <v>7158679</v>
+        <v>7158656</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2955,17 +2882,12 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2024-05-01</t>
+          <t>2025-07-03</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2024-05-01</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Datum osäkert, men mellan 2024-05-05 och 2025-10-47</t>
+          <t>2025-07-03</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2980,22 +2902,22 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Lukas Holmström</t>
+          <t>Manne Frih</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Lukas Holmström</t>
+          <t>Manne Frih</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>133851027</v>
+        <v>133850741</v>
       </c>
       <c r="B24" t="n">
-        <v>91987</v>
+        <v>83358</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3003,19 +2925,23 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>5432</v>
+        <v>6440</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H24" t="inlineStr"/>
+          <t>Chaenotheca subroscida</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
@@ -3023,10 +2949,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>611709</v>
+        <v>611694</v>
       </c>
       <c r="R24" t="n">
-        <v>7158385</v>
+        <v>7158620</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3063,7 +2989,7 @@
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>Datum osäkert, men mellan 2024-05-05 och 2025-10-47</t>
+          <t>Datum osäkert, men mellan 2024-05-05 och 2025-10-82</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3090,10 +3016,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>133850797</v>
+        <v>126382400</v>
       </c>
       <c r="B25" t="n">
-        <v>91967</v>
+        <v>57953</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3101,37 +3027,37 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Skogen, Ås lm</t>
+          <t>Bredmyran, Bredmyran, Ås lm</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>611695</v>
+        <v>611773</v>
       </c>
       <c r="R25" t="n">
-        <v>7158387</v>
+        <v>7158412</v>
       </c>
       <c r="S25" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3155,17 +3081,27 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2024-05-01</t>
+          <t>2025-07-03</t>
+        </is>
+      </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>10:55</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2024-05-01</t>
+          <t>2025-07-03</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>10:55</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>Datum osäkert, men mellan 2024-05-05 och 2025-10-33</t>
+          <t>Färsk ringhack yngre än 5 år</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3180,22 +3116,22 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Lukas Holmström</t>
+          <t>Carl Wiking</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Lukas Holmström</t>
+          <t>Carl Wiking</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>133850775</v>
+        <v>126382580</v>
       </c>
       <c r="B26" t="n">
-        <v>91967</v>
+        <v>57953</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3203,37 +3139,37 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Skogen, Ås lm</t>
+          <t>Riprismyrtjärnen, Riprismyrtjärnen, Ås lm</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>611818</v>
+        <v>611675</v>
       </c>
       <c r="R26" t="n">
-        <v>7158675</v>
+        <v>7158457</v>
       </c>
       <c r="S26" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3257,17 +3193,27 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2024-05-01</t>
+          <t>2025-07-03</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2024-05-01</t>
+          <t>2025-07-03</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>Datum osäkert, men mellan 2024-05-05 och 2025-10-53</t>
+          <t>Tretåig hackspett yngre än 5 år</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3282,22 +3228,22 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Lukas Holmström</t>
+          <t>Carl Wiking</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Lukas Holmström</t>
+          <t>Carl Wiking</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>133850778</v>
+        <v>126383064</v>
       </c>
       <c r="B27" t="n">
-        <v>91967</v>
+        <v>57953</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3305,37 +3251,42 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Skogen, Ås lm</t>
+          <t>Bredmyran, Bredmyran, Ås lm</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>611840</v>
+        <v>611800</v>
       </c>
       <c r="R27" t="n">
-        <v>7158308</v>
+        <v>7158320</v>
       </c>
       <c r="S27" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3359,17 +3310,22 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2024-05-01</t>
+          <t>2025-07-03</t>
+        </is>
+      </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>10:18</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2024-05-01</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>Datum osäkert, men mellan 2024-05-05 och 2025-10-51</t>
+          <t>2025-07-03</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>10:18</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3384,22 +3340,22 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Lukas Holmström</t>
+          <t>Tove Lundmark</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Lukas Holmström</t>
+          <t>Tove Lundmark</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>133851001</v>
+        <v>126383125</v>
       </c>
       <c r="B28" t="n">
-        <v>91963</v>
+        <v>57953</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3407,37 +3363,42 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Skogen, Ås lm</t>
+          <t>Bredmyran, Bredmyran, Ås lm</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>611791</v>
+        <v>611839</v>
       </c>
       <c r="R28" t="n">
-        <v>7158655</v>
+        <v>7158341</v>
       </c>
       <c r="S28" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3461,17 +3422,22 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2024-05-01</t>
+          <t>2025-07-03</t>
+        </is>
+      </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2024-05-01</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>Datum osäkert, men mellan 2024-05-05 och 2025-10-70</t>
+          <t>2025-07-03</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3486,22 +3452,22 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Lukas Holmström</t>
+          <t>Tove Lundmark</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Lukas Holmström</t>
+          <t>Tove Lundmark</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>133850741</v>
+        <v>126384755</v>
       </c>
       <c r="B29" t="n">
-        <v>83351</v>
+        <v>57953</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3509,37 +3475,37 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6440</v>
+        <v>100109</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Skogen, Ås lm</t>
+          <t>Riprismyrtjärnen, Riprismyrtjärnen, Ås lm</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>611694</v>
+        <v>611634</v>
       </c>
       <c r="R29" t="n">
-        <v>7158620</v>
+        <v>7158666</v>
       </c>
       <c r="S29" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3563,17 +3529,22 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2024-05-01</t>
+          <t>2025-07-03</t>
+        </is>
+      </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2024-05-01</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Datum osäkert, men mellan 2024-05-05 och 2025-10-82</t>
+          <t>2025-07-03</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3588,22 +3559,22 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Lukas Holmström</t>
+          <t>Tove Lundmark</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Lukas Holmström</t>
+          <t>Tove Lundmark</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>133851042</v>
+        <v>126390901</v>
       </c>
       <c r="B30" t="n">
-        <v>91987</v>
+        <v>57953</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3611,30 +3582,42 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H30" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Skogen, Ås lm</t>
+          <t>Riprismyrtjärnen, Ås lm</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>611683</v>
+        <v>611763</v>
       </c>
       <c r="R30" t="n">
-        <v>7158448</v>
+        <v>7158409</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3661,17 +3644,12 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2024-05-01</t>
+          <t>2025-07-03</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2024-05-01</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Datum osäkert, men mellan 2024-05-05 och 2025-10-32</t>
+          <t>2025-07-03</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3686,57 +3664,57 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Lukas Holmström</t>
+          <t>Manne Frih</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Lukas Holmström</t>
+          <t>Manne Frih</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>133850794</v>
+        <v>126390900</v>
       </c>
       <c r="B31" t="n">
-        <v>91967</v>
+        <v>5179</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1202</v>
+        <v>100526</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Skogen, Ås lm</t>
+          <t>Riprismyrtjärnen, Ås lm</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>611791</v>
+        <v>611671</v>
       </c>
       <c r="R31" t="n">
-        <v>7158655</v>
+        <v>7158434</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3763,17 +3741,12 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2024-05-01</t>
+          <t>2025-07-03</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2024-05-01</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>Datum osäkert, men mellan 2024-05-05 och 2025-10-36</t>
+          <t>2025-07-03</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3788,57 +3761,57 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Lukas Holmström</t>
+          <t>Manne Frih</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Lukas Holmström</t>
+          <t>Manne Frih</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>133851104</v>
+        <v>126390902</v>
       </c>
       <c r="B32" t="n">
-        <v>83343</v>
+        <v>5199</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>308</v>
+        <v>105930</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Skogen, Ås lm</t>
+          <t>Riprismyrtjärnen, Ås lm</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>611745</v>
+        <v>611913</v>
       </c>
       <c r="R32" t="n">
-        <v>7158685</v>
+        <v>7158583</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3865,17 +3838,12 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2024-05-01</t>
+          <t>2025-07-03</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2024-05-01</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>Datum osäkert, men mellan 2024-05-05 och 2025-10-46</t>
+          <t>2025-07-03</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3890,117 +3858,15 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Lukas Holmström</t>
+          <t>Manne Frih</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Lukas Holmström</t>
+          <t>Manne Frih</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
-    </row>
-    <row r="33">
-      <c r="A33" t="n">
-        <v>133850774</v>
-      </c>
-      <c r="B33" t="n">
-        <v>91967</v>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E33" t="n">
-        <v>1202</v>
-      </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>Ullticka</t>
-        </is>
-      </c>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t>Phellinidium ferrugineofuscum</t>
-        </is>
-      </c>
-      <c r="H33" t="inlineStr">
-        <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr"/>
-      <c r="P33" t="inlineStr">
-        <is>
-          <t>Skogen, Ås lm</t>
-        </is>
-      </c>
-      <c r="Q33" t="n">
-        <v>611669</v>
-      </c>
-      <c r="R33" t="n">
-        <v>7158675</v>
-      </c>
-      <c r="S33" t="n">
-        <v>10</v>
-      </c>
-      <c r="T33" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U33" t="inlineStr">
-        <is>
-          <t>Vilhelmina</t>
-        </is>
-      </c>
-      <c r="V33" t="inlineStr">
-        <is>
-          <t>Åsele lappmark</t>
-        </is>
-      </c>
-      <c r="W33" t="inlineStr">
-        <is>
-          <t>Vilhelmina</t>
-        </is>
-      </c>
-      <c r="Y33" t="inlineStr">
-        <is>
-          <t>2024-05-01</t>
-        </is>
-      </c>
-      <c r="AA33" t="inlineStr">
-        <is>
-          <t>2024-05-01</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>Datum osäkert, men mellan 2024-05-05 och 2025-10-54</t>
-        </is>
-      </c>
-      <c r="AD33" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE33" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG33" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT33" t="inlineStr"/>
-      <c r="AW33" t="inlineStr">
-        <is>
-          <t>Lukas Holmström</t>
-        </is>
-      </c>
-      <c r="AX33" t="inlineStr">
-        <is>
-          <t>Lukas Holmström</t>
-        </is>
-      </c>
-      <c r="AY33" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
